--- a/ALL/p05-out/Recipes.xlsx
+++ b/ALL/p05-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,45 +439,165 @@
           <t>Recipe</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Generated At</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Json Recipe</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt Image Ingredients</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>Classic Vegetable Stir Fry</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pizza Delight 🍕✨
+          <t>Classic Vegetable Stir Fry 🥦🍜
 Ingredients:
-- 2 cups all-purpose flour
-- 1 packet (2 ¼ tsp) active dry yeast
-- ¾ cup warm water
-- 1 tsp sugar
-- 1 tsp salt
-- 1 tbsp olive oil
-- 1 cup marinara sauce
-- 1 ½ cups shredded mozzarella cheese
-- ½ cup sliced pepperoni
-- 1 tsp dried oregano
+- 2 cups mixed bell peppers, sliced
+- 1 cup broccoli florets
+- 1 cup snap peas
+- 1 medium carrot, julienned
+- 2 tablespoons vegetable oil
+- 3 cloves garlic, minced
+- 1 inch ginger, grated
+- 2 tablespoons soy sauce
+- 1 tablespoon sesame oil
+- 1 teaspoon sesame seeds (for garnish)
 Instructions:
-1. In a small bowl, combine warm water, sugar, and yeast. Let it sit for about 5 minutes until frothy.
-2. In a large mixing bowl, combine flour and salt. Create a well in the center and add the yeast mixture and olive oil.
-3. Mix until a dough forms, then knead for about 5-7 minutes until smooth and elastic.
-4. Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm place for 1 hour or until doubled in size.
-5. Preheat your oven to 475°F (245°C).
-6. Roll out the dough on a floured surface to your desired thickness and shape. Transfer to a pizza stone or baking sheet.
-7. Spread marinara sauce evenly over the dough, leaving a small border around the edges.
-8. Sprinkle mozzarella cheese on top of the sauce, then layer with pepperoni and sprinkle oregano.
-9. Bake in the preheated oven for 12-15 minutes until the crust is golden and the cheese is bubbly.
-10. Remove from the oven, let it cool slightly, slice, and serve.
-Prep Time: 15 minutes
-Cook Time: 15 minutes
-Total Time: 1 hour 30 minutes
+1. Heat the vegetable oil in a large skillet or wok over medium-high heat.
+2. Add the minced garlic and grated ginger, sautéing for about 30 seconds until fragrant.
+3. Add the sliced bell peppers, broccoli florets, and julienned carrot to the skillet. Stir-fry for 3-4 minutes until they begin to soften.
+4. Toss in the snap peas and continue to stir-fry for another 2-3 minutes.
+5. Pour in the soy sauce and sesame oil, stirring to coat the vegetables evenly.
+6. Cook for an additional 1-2 minutes, allowing the sauce to thicken slightly.
+7. Remove from heat and sprinkle with sesame seeds for garnish.
+8. Serve hot over steamed rice or noodles.
+Prep Time: 10 minutes
+Cook Time: 10 minutes
+Total Time: 20 minutes
 Course: Main Course
-Cuisine: Italian
+Cuisine: Asian
 Servings: 4
-Calories: ~350 per serving</t>
+Calories: ~220 per serving</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:07:23</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{
+  "name": "Classic Vegetable Stir Fry",
+  "summary": "A quick and colorful stir fry featuring a variety of fresh vegetables, perfect for a healthy meal. This dish is packed with flavor and can be served over rice or noodles.",
+  "servings": "4",
+  "prep_time": "10",
+  "cook_time": "10",
+  "total_time": "20",
+  "calories": "220",
+  "course": "Main Course",
+  "cuisine": "Asian",
+  "keywords": [
+    "vegetable",
+    "stir fry",
+    "quick",
+    "healthy",
+    "colorful",
+    "easy",
+    "Asian"
+  ],
+  "notes": "Serve hot for the best flavor. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "2",
+      "unit": "cups",
+      "name": "mixed bell peppers, sliced"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "broccoli florets"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "snap peas"
+    },
+    {
+      "amount": "1",
+      "unit": "medium",
+      "name": "carrot, julienned"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "vegetable oil"
+    },
+    {
+      "amount": "3",
+      "unit": "cloves",
+      "name": "garlic, minced"
+    },
+    {
+      "amount": "1",
+      "unit": "inch",
+      "name": "ginger, grated"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "soy sauce"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "sesame oil"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "sesame seeds (for garnish)"
+    }
+  ],
+  "instructions": [
+    "Heat the vegetable oil in a large skillet or wok over medium-high heat.",
+    "Add the minced garlic and grated ginger, sautéing for about 30 seconds until fragrant.",
+    "Add the sliced bell peppers, broccoli florets, and julienned carrot to the skillet. Stir-fry for 3-4 minutes until they begin to soften.",
+    "Toss in the snap peas and continue to stir-fry for another 2-3 minutes.",
+    "Pour in the soy sauce and sesame oil, stirring to coat the vegetables evenly.",
+    "Cook for an additional 1-2 minutes, allowing the sauce to thicken slightly.",
+    "Remove from heat and sprinkle with sesame seeds for garnish.",
+    "Serve hot over steamed rice or noodles."
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Realistic, appetizing ULTRA close-up of a vibrant vegetable stir fry featuring mixed bell peppers, broccoli florets, snap peas, and julienned carrots, glistening with soy sauce and sesame oil, garnished with sesame seeds, served in a clean white ceramic bowl on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at food center, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>mixed bell peppers, broccoli, snap peas, carrot, vegetable oil, garlic, ginger, soy sauce, sesame oil, sesame seeds, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
     </row>
